--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tickets'!$A$1:$N$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 1 in progress, 5 to do.</t>
+          <t>Rolled up from 6 children: 2 in progress, 4 to do.</t>
         </is>
       </c>
       <c r="G109" s="20" t="inlineStr">
@@ -10526,14 +10526,14 @@
           <t>Own the JWT secret and the API keys</t>
         </is>
       </c>
-      <c r="E119" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E119" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 to do.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
         </is>
       </c>
       <c r="G119" s="20" t="inlineStr">
@@ -10598,14 +10598,14 @@
           <t>Key generation and rotation runbook</t>
         </is>
       </c>
-      <c r="E120" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E120" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>infra/modules/keys, scripts/platform-keys.mjs, docs/runbooks/api-keys.md; plan row 5.7.</t>
         </is>
       </c>
       <c r="G120" s="20" t="inlineStr">
@@ -11021,7 +11021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 1 in progress, 5 to do.</t>
+          <t>Rolled up from 6 children: 2 in progress, 4 to do.</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -12898,14 +12898,14 @@
           <t>Own the JWT secret and the API keys</t>
         </is>
       </c>
-      <c r="D43" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 to do.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -13120,7 +13120,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="C48" s="23" t="inlineStr">
         <is>
-          <t>Key generation and rotation runbook</t>
+          <t>Expose auth and REST through the load balancer</t>
         </is>
       </c>
       <c r="D48" s="25" t="inlineStr">
@@ -13167,17 +13167,17 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr">
         <is>
-          <t>Expose auth and REST through the load balancer</t>
+          <t>Cutover and decommission</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Rolled up from 2 children: 2 to do.</t>
         </is>
       </c>
       <c r="F49" s="20" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="H49" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I49" s="20" t="inlineStr">
@@ -13214,17 +13214,17 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C50" s="23" t="inlineStr">
         <is>
-          <t>Cutover and decommission</t>
+          <t>Update the documentation</t>
         </is>
       </c>
       <c r="D50" s="25" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 to do.</t>
+          <t>Stage 5, added 17 September 2026.</t>
         </is>
       </c>
       <c r="F50" s="20" t="inlineStr">
@@ -13254,77 +13254,30 @@
       </c>
       <c r="I50" s="20" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C51" s="23" t="inlineStr">
-        <is>
-          <t>Update the documentation</t>
-        </is>
-      </c>
-      <c r="D51" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="inlineStr">
-        <is>
-          <t>Stage 5, added 17 September 2026.</t>
-        </is>
-      </c>
-      <c r="F51" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G51" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H51" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I51" s="20" t="inlineStr">
-        <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Open tickets</t>
+        </is>
+      </c>
+      <c r="B52" s="7">
+        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
+        <v/>
+      </c>
+    </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Open tickets</t>
-        </is>
-      </c>
-      <c r="B53" s="7">
-        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>The rows are a snapshot; the count beside them is live from the Tickets sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I51"/>
+  <autoFilter ref="A4:I50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tickets'!$A$1:$N$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 2 in progress, 4 to do.</t>
+          <t>Rolled up from 6 children: 3 in progress, 3 to do.</t>
         </is>
       </c>
       <c r="G109" s="20" t="inlineStr">
@@ -10094,14 +10094,14 @@
           <t>PostgREST as an ECS service</t>
         </is>
       </c>
-      <c r="E113" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E113" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 to do.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
         </is>
       </c>
       <c r="G113" s="20" t="inlineStr">
@@ -10166,14 +10166,14 @@
           <t>PostgREST task definition and service</t>
         </is>
       </c>
-      <c r="E114" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E114" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>infra/modules/postgrest and the service_role RLS policy migration; plan row 5.3.</t>
         </is>
       </c>
       <c r="G114" s="20" t="inlineStr">
@@ -11021,7 +11021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 2 in progress, 4 to do.</t>
+          <t>Rolled up from 6 children: 3 in progress, 3 to do.</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -12710,14 +12710,14 @@
           <t>PostgREST as an ECS service</t>
         </is>
       </c>
-      <c r="D39" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 to do.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
@@ -12744,17 +12744,17 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>PostgREST task definition and service</t>
+          <t>GoTrue as an ECS service</t>
         </is>
       </c>
       <c r="D40" s="25" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Rolled up from 3 children: 3 to do.</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -12791,17 +12791,17 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>GoTrue as an ECS service</t>
+          <t>GoTrue task definition and service</t>
         </is>
       </c>
       <c r="D41" s="25" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 3 to do.</t>
+          <t>Stage 5, added 17 September 2026.</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -12838,27 +12838,27 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>GoTrue task definition and service</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Own the JWT secret and the API keys</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
@@ -12885,7 +12885,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -12895,17 +12895,17 @@
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>Own the JWT secret and the API keys</t>
-        </is>
-      </c>
-      <c r="D43" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Routing and configuration cutover</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
+          <t>Rolled up from 1 child: 1 to do.</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -12932,17 +12932,17 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>Routing and configuration cutover</t>
+          <t>Rehearse the cutover and the rollback</t>
         </is>
       </c>
       <c r="D44" s="25" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 to do.</t>
+          <t>Stage 5, added 17 September 2026.</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
@@ -12979,7 +12979,7 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>Rehearse the cutover and the rollback</t>
+          <t>Auth email through SES</t>
         </is>
       </c>
       <c r="D45" s="25" t="inlineStr">
@@ -13019,14 +13019,14 @@
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>Auth email through SES</t>
+          <t>Carry the Google OAuth provider across</t>
         </is>
       </c>
       <c r="D46" s="25" t="inlineStr">
@@ -13073,7 +13073,7 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>Carry the Google OAuth provider across</t>
+          <t>Expose auth and REST through the load balancer</t>
         </is>
       </c>
       <c r="D47" s="25" t="inlineStr">
@@ -13120,17 +13120,17 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C48" s="23" t="inlineStr">
         <is>
-          <t>Expose auth and REST through the load balancer</t>
+          <t>Cutover and decommission</t>
         </is>
       </c>
       <c r="D48" s="25" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Rolled up from 2 children: 2 to do.</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="H48" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I48" s="20" t="inlineStr">
@@ -13167,17 +13167,17 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr">
         <is>
-          <t>Cutover and decommission</t>
+          <t>Update the documentation</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 to do.</t>
+          <t>Stage 5, added 17 September 2026.</t>
         </is>
       </c>
       <c r="F49" s="20" t="inlineStr">
@@ -13207,77 +13207,30 @@
       </c>
       <c r="I49" s="20" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="B50" s="20" t="inlineStr">
-        <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C50" s="23" t="inlineStr">
-        <is>
-          <t>Update the documentation</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E50" s="23" t="inlineStr">
-        <is>
-          <t>Stage 5, added 17 September 2026.</t>
-        </is>
-      </c>
-      <c r="F50" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G50" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H50" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I50" s="20" t="inlineStr">
-        <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Open tickets</t>
+        </is>
+      </c>
+      <c r="B51" s="7">
+        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
+        <v/>
+      </c>
+    </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Open tickets</t>
-        </is>
-      </c>
-      <c r="B52" s="7">
-        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>The rows are a snapshot; the count beside them is live from the Tickets sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I50"/>
+  <autoFilter ref="A4:I49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tickets'!$A$1:$N$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 3 in progress, 3 to do.</t>
+          <t>Rolled up from 6 children: 4 in progress, 2 to do.</t>
         </is>
       </c>
       <c r="G109" s="20" t="inlineStr">
@@ -10238,14 +10238,14 @@
           <t>GoTrue as an ECS service</t>
         </is>
       </c>
-      <c r="E115" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E115" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 3 to do.</t>
+          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
         </is>
       </c>
       <c r="G115" s="20" t="inlineStr">
@@ -10310,14 +10310,14 @@
           <t>GoTrue task definition and service</t>
         </is>
       </c>
-      <c r="E116" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E116" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>infra/modules/gotrue; plan row 5.4.</t>
         </is>
       </c>
       <c r="G116" s="20" t="inlineStr">
@@ -10382,14 +10382,14 @@
           <t>Auth email through SES</t>
         </is>
       </c>
-      <c r="E117" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E117" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
         </is>
       </c>
       <c r="G117" s="20" t="inlineStr">
@@ -10454,14 +10454,14 @@
           <t>Carry the Google OAuth provider across</t>
         </is>
       </c>
-      <c r="E118" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E118" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
         </is>
       </c>
       <c r="G118" s="20" t="inlineStr">
@@ -11021,7 +11021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 3 in progress, 3 to do.</t>
+          <t>Rolled up from 6 children: 4 in progress, 2 to do.</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -12757,14 +12757,14 @@
           <t>GoTrue as an ECS service</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 3 to do.</t>
+          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -12791,27 +12791,27 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>GoTrue task definition and service</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Own the JWT secret and the API keys</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -12838,7 +12838,7 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
@@ -12848,17 +12848,17 @@
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>Own the JWT secret and the API keys</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Routing and configuration cutover</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
+          <t>Rolled up from 1 child: 1 to do.</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
@@ -12885,17 +12885,17 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>Routing and configuration cutover</t>
+          <t>Rehearse the cutover and the rollback</t>
         </is>
       </c>
       <c r="D43" s="25" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 to do.</t>
+          <t>Stage 5, added 17 September 2026.</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -12932,7 +12932,7 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
@@ -12942,17 +12942,17 @@
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>Rehearse the cutover and the rollback</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Auth email through SES</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
@@ -12972,14 +12972,14 @@
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
@@ -12989,17 +12989,17 @@
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>Auth email through SES</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Carry the Google OAuth provider across</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
@@ -13026,7 +13026,7 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>Carry the Google OAuth provider across</t>
+          <t>Expose auth and REST through the load balancer</t>
         </is>
       </c>
       <c r="D46" s="25" t="inlineStr">
@@ -13073,17 +13073,17 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>Expose auth and REST through the load balancer</t>
+          <t>Cutover and decommission</t>
         </is>
       </c>
       <c r="D47" s="25" t="inlineStr">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Rolled up from 2 children: 2 to do.</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="H47" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I47" s="20" t="inlineStr">
@@ -13120,17 +13120,17 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C48" s="23" t="inlineStr">
         <is>
-          <t>Cutover and decommission</t>
+          <t>Update the documentation</t>
         </is>
       </c>
       <c r="D48" s="25" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 to do.</t>
+          <t>Stage 5, added 17 September 2026.</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
@@ -13160,77 +13160,30 @@
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
-          <t>Update the documentation</t>
-        </is>
-      </c>
-      <c r="D49" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="inlineStr">
-        <is>
-          <t>Stage 5, added 17 September 2026.</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G49" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H49" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I49" s="20" t="inlineStr">
-        <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Open tickets</t>
+        </is>
+      </c>
+      <c r="B50" s="7">
+        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
+        <v/>
+      </c>
+    </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Open tickets</t>
-        </is>
-      </c>
-      <c r="B51" s="7">
-        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>The rows are a snapshot; the count beside them is live from the Tickets sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I49"/>
+  <autoFilter ref="A4:I48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tickets'!$A$1:$N$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 4 in progress, 2 to do.</t>
+          <t>Rolled up from 6 children: 5 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="G109" s="20" t="inlineStr">
@@ -10670,14 +10670,14 @@
           <t>Routing and configuration cutover</t>
         </is>
       </c>
-      <c r="E121" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E121" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 to do.</t>
+          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
         </is>
       </c>
       <c r="G121" s="20" t="inlineStr">
@@ -10742,14 +10742,14 @@
           <t>Expose auth and REST through the load balancer</t>
         </is>
       </c>
-      <c r="E122" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E122" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>frontend module: platform origins, behaviours and prefix function on platform_enabled; plan row 5.8.</t>
         </is>
       </c>
       <c r="G122" s="20" t="inlineStr">
@@ -11021,7 +11021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 4 in progress, 2 to do.</t>
+          <t>Rolled up from 6 children: 5 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -12851,14 +12851,14 @@
           <t>Routing and configuration cutover</t>
         </is>
       </c>
-      <c r="D42" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 to do.</t>
+          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
@@ -13026,17 +13026,17 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>Expose auth and REST through the load balancer</t>
+          <t>Cutover and decommission</t>
         </is>
       </c>
       <c r="D46" s="25" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Rolled up from 2 children: 2 to do.</t>
         </is>
       </c>
       <c r="F46" s="20" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="H46" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I46" s="20" t="inlineStr">
@@ -13073,17 +13073,17 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>Cutover and decommission</t>
+          <t>Update the documentation</t>
         </is>
       </c>
       <c r="D47" s="25" t="inlineStr">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 to do.</t>
+          <t>Stage 5, added 17 September 2026.</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
@@ -13113,77 +13113,30 @@
       </c>
       <c r="I47" s="20" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="inlineStr">
-        <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C48" s="23" t="inlineStr">
-        <is>
-          <t>Update the documentation</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E48" s="23" t="inlineStr">
-        <is>
-          <t>Stage 5, added 17 September 2026.</t>
-        </is>
-      </c>
-      <c r="F48" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G48" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H48" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I48" s="20" t="inlineStr">
-        <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Open tickets</t>
+        </is>
+      </c>
+      <c r="B49" s="7">
+        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
+        <v/>
+      </c>
+    </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Open tickets</t>
-        </is>
-      </c>
-      <c r="B50" s="7">
-        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>The rows are a snapshot; the count beside them is live from the Tickets sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I48"/>
+  <autoFilter ref="A4:I47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tickets'!$A$1:$N$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 5 in progress, 1 to do.</t>
+          <t>Rolled up from 6 children: 1 done, 4 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="G109" s="20" t="inlineStr">
@@ -9878,14 +9878,14 @@
           <t>Postgres on RDS</t>
         </is>
       </c>
-      <c r="E110" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="E110" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 done, 1 to do.</t>
+          <t>Rolled up from 2 children: 2 done.</t>
         </is>
       </c>
       <c r="G110" s="20" t="inlineStr">
@@ -10022,14 +10022,14 @@
           <t>Dump and restore, including the auth schema</t>
         </is>
       </c>
-      <c r="E112" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E112" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>infra/dbtools image and module, docs/runbooks/platform-migration.md; plan row 5.2. The acceptance criteria are proven at the rehearsal (2125).</t>
         </is>
       </c>
       <c r="G112" s="20" t="inlineStr">
@@ -11021,7 +11021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 5 in progress, 1 to do.</t>
+          <t>Rolled up from 6 children: 1 done, 4 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -12603,7 +12603,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>Postgres on RDS</t>
+          <t>PostgREST as an ECS service</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 done, 1 to do.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -12650,27 +12650,27 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>Dump and restore, including the auth schema</t>
-        </is>
-      </c>
-      <c r="D38" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>GoTrue as an ECS service</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="H38" s="20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I38" s="20" t="inlineStr">
@@ -12697,7 +12697,7 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="C39" s="23" t="inlineStr">
         <is>
-          <t>PostgREST as an ECS service</t>
+          <t>Own the JWT secret and the API keys</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
@@ -12744,7 +12744,7 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>GoTrue as an ECS service</t>
+          <t>Routing and configuration cutover</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
+          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -12791,27 +12791,27 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>Own the JWT secret and the API keys</t>
-        </is>
-      </c>
-      <c r="D41" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Rehearse the cutover and the rollback</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
+          <t>Stage 5, added 17 September 2026.</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -12838,17 +12838,17 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>Routing and configuration cutover</t>
+          <t>Auth email through SES</t>
         </is>
       </c>
       <c r="D42" s="22" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
+          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
@@ -12878,14 +12878,14 @@
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -12895,17 +12895,17 @@
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>Rehearse the cutover and the rollback</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Carry the Google OAuth provider across</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -12925,34 +12925,34 @@
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>Auth email through SES</t>
-        </is>
-      </c>
-      <c r="D44" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Cutover and decommission</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
+          <t>Rolled up from 2 children: 2 to do.</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="H44" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I44" s="20" t="inlineStr">
@@ -12979,7 +12979,7 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
@@ -12989,17 +12989,17 @@
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>Carry the Google OAuth provider across</t>
-        </is>
-      </c>
-      <c r="D45" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Update the documentation</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
+          <t>Stage 5, added 17 September 2026.</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
@@ -13014,129 +13014,35 @@
       </c>
       <c r="H45" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2124</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C46" s="23" t="inlineStr">
-        <is>
-          <t>Cutover and decommission</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E46" s="23" t="inlineStr">
-        <is>
-          <t>Rolled up from 2 children: 2 to do.</t>
-        </is>
-      </c>
-      <c r="F46" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G46" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H46" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I46" s="20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="inlineStr">
-        <is>
-          <t>Update the documentation</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>Stage 5, added 17 September 2026.</t>
-        </is>
-      </c>
-      <c r="F47" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G47" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H47" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I47" s="20" t="inlineStr">
-        <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Open tickets</t>
         </is>
       </c>
-      <c r="B49" s="7">
+      <c r="B47" s="7">
         <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>The rows are a snapshot; the count beside them is live from the Tickets sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I47"/>
+  <autoFilter ref="A4:I45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 1 done, 4 in progress, 1 to do.</t>
+          <t>Rolled up from 6 children: 1 done, 5 in progress.</t>
         </is>
       </c>
       <c r="G109" s="20" t="inlineStr">
@@ -10814,14 +10814,14 @@
           <t>Cutover and decommission</t>
         </is>
       </c>
-      <c r="E123" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E123" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 to do.</t>
+          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="G123" s="20" t="inlineStr">
@@ -10886,14 +10886,14 @@
           <t>Rehearse the cutover and the rollback</t>
         </is>
       </c>
-      <c r="E124" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E124" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Procedure written (docs/runbooks/platform-cutover.md) and the smoke test extended; the rehearsal itself needs the applied platform and Stage 5, Tasks 1 to 4.</t>
         </is>
       </c>
       <c r="G124" s="20" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 1 done, 4 in progress, 1 to do.</t>
+          <t>Rolled up from 6 children: 1 done, 5 in progress.</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -12804,14 +12804,14 @@
           <t>Rehearse the cutover and the rollback</t>
         </is>
       </c>
-      <c r="D41" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>Procedure written (docs/runbooks/platform-cutover.md) and the smoke test extended; the rehearsal itself needs the applied platform and Stage 5, Tasks 1 to 4.</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -12945,14 +12945,14 @@
           <t>Cutover and decommission</t>
         </is>
       </c>
-      <c r="D44" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 to do.</t>
+          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">

--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -10821,7 +10821,7 @@
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="G123" s="20" t="inlineStr">
@@ -10958,14 +10958,14 @@
           <t>Update the documentation</t>
         </is>
       </c>
-      <c r="E125" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E125" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>The platform is documented beside Supabase (plan row 5.10); the pass that removes the Supabase paragraphs waits for Stage 5, Task 6.</t>
         </is>
       </c>
       <c r="G125" s="20" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
@@ -12992,14 +12992,14 @@
           <t>Update the documentation</t>
         </is>
       </c>
-      <c r="D45" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>Stage 5, added 17 September 2026.</t>
+          <t>The platform is documented beside Supabase (plan row 5.10); the pass that removes the Supabase paragraphs waits for Stage 5, Task 6.</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">

--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -62,13 +62,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00434343"/>
+      <color rgb="00990000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00990000"/>
+      <color rgb="00434343"/>
       <sz val="10"/>
     </font>
     <font>
@@ -126,12 +126,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EAED"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00E8EAED"/>
       </patternFill>
     </fill>
     <fill>
@@ -205,7 +205,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,7 +214,7 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2730,14 +2730,14 @@
           <t>Run a first upstream merge as a dry run</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Never performed in this fork; the "upstream" merges in history are inherited. Value decays as the fork diverges.</t>
+          <t>Rehearsed in a scratch worktree on 17 September 2026 and sized in docs/upstream-sync.md ("The first sync, sized"): 49 conflicts, four of them decisions against fork positions, plus 40 files to debrand. Recommended as its own sprint.</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -2942,7 +2942,7 @@
           <t>Replace xlsx with exceljs in spreadsheet.ts</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>Won't do</t>
         </is>
@@ -3086,7 +3086,7 @@
           <t>Take ownership of the workflow catalogue</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -3158,7 +3158,7 @@
           <t>Fork mike-workflows and repoint the sync</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -3230,7 +3230,7 @@
           <t>Verify catalogue sync end to end</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -3730,7 +3730,7 @@
           <t>Disable the Word add-in workflow while the add-in is deferred</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>Won't do</t>
         </is>
@@ -9166,7 +9166,7 @@
           <t>Address what the load test surfaces</t>
         </is>
       </c>
-      <c r="E100" s="25" t="inlineStr">
+      <c r="E100" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9378,7 +9378,7 @@
           <t>Run the full suite against production configuration</t>
         </is>
       </c>
-      <c r="E103" s="25" t="inlineStr">
+      <c r="E103" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9738,7 +9738,7 @@
           <t>Post-launch monitoring window</t>
         </is>
       </c>
-      <c r="E108" s="25" t="inlineStr">
+      <c r="E108" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11253,7 +11253,7 @@
           <t>Take ownership of the workflow catalogue</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11300,7 +11300,7 @@
           <t>Fork mike-workflows and repoint the sync</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11347,14 +11347,14 @@
           <t>Run a first upstream merge as a dry run</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Never performed in this fork; the "upstream" merges in history are inherited. Value decays as the fork diverges.</t>
+          <t>Rehearsed in a scratch worktree on 17 September 2026 and sized in docs/upstream-sync.md ("The first sync, sized"): 49 conflicts, four of them decisions against fork positions, plus 40 files to debrand. Recommended as its own sprint.</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -11394,7 +11394,7 @@
           <t>Verify catalogue sync end to end</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -12099,7 +12099,7 @@
           <t>Run the full suite against production configuration</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -12334,7 +12334,7 @@
           <t>Post-launch monitoring window</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -12522,7 +12522,7 @@
           <t>Address what the load test surfaces</t>
         </is>
       </c>
-      <c r="D35" s="25" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>To do</t>
         </is>

--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -3165,7 +3165,7 @@
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Inherited from parent 2014 (to do).</t>
+          <t>Licence checked 17 September 2026: the catalogue repository is MIT (outstanding.md). The fork itself needs an account only the operator controls; after it, two tfvars values and an apply.</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>Inherited from parent 2014 (to do).</t>
+          <t>Licence checked 17 September 2026: the catalogue repository is MIT (outstanding.md). The fork itself needs an account only the operator controls; after it, two tfvars values and an apply.</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">

--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tickets'!$A$1:$N$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9450,14 +9450,14 @@
           <t>Sign off the licence compliance checklist</t>
         </is>
       </c>
-      <c r="E104" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="E104" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>Signed off against the running production service on 18 September 2026 at 78b795b6; see docs/licence-compliance.md, "Signed off against production". Item 5's manual half is discharged.</t>
         </is>
       </c>
       <c r="G104" s="20" t="inlineStr">
@@ -9666,14 +9666,14 @@
           <t>Production cutover and smoke test</t>
         </is>
       </c>
-      <c r="E107" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="E107" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>As 2105.</t>
+          <t>Smoke tested against the live service on 18 September 2026: 6 of 6 checks pass and the source link resolves to the mirror at the running commit. The run found two defects in the smoke test itself, both fixed.</t>
         </is>
       </c>
       <c r="G107" s="20" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>Alarms are armed (16, all with actions) but both SNS alert topics have zero subscriptions, so nothing would reach anyone. Needs an address subscribed and confirmed before the window can start.</t>
         </is>
       </c>
       <c r="G108" s="20" t="inlineStr">
@@ -11021,7 +11021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12133,7 +12133,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>Sign off the licence compliance checklist</t>
+          <t>Security review of the combined deployment</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>This repository half done: 3 findings, all fixed. Juralio side and the seam from its end outstanding.</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -12180,17 +12180,17 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>Security review of the combined deployment</t>
+          <t>Go live</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>This repository half done: 3 findings, all fixed. Juralio side and the seam from its end outstanding.</t>
+          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -12227,27 +12227,27 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>Go live</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Post-launch monitoring window</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
+          <t>Alarms are armed (16, all with actions) but both SNS alert topics have zero subscriptions, so nothing would reach anyone. Needs an address subscribed and confirmed before the window can start.</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -12274,17 +12274,17 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>Production cutover and smoke test</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>Operational readiness</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>As 2105.</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -12309,39 +12309,39 @@
       </c>
       <c r="H30" s="20" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>Post-launch monitoring window</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Performance and resilience</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -12356,29 +12356,29 @@
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>Operational readiness</t>
+          <t>Sub-task</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>Run the k6 SSE load scenario against staging</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 in progress.</t>
+          <t>As 2097.</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -12403,39 +12403,39 @@
       </c>
       <c r="H32" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>Performance and resilience</t>
-        </is>
-      </c>
-      <c r="D33" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Address what the load test surfaces</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
+          <t>From the delivery plan row that cites it.</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -12462,17 +12462,17 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>Run the k6 SSE load scenario against staging</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>Run the platform services on AWS instead of Supabase</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -12482,91 +12482,91 @@
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>As 2097.</t>
+          <t>Rolled up from 6 children: 1 done, 5 in progress.</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>Phase 3 - Production Ready</t>
+          <t>Phase 4 - Self-hosted platform</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 7</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>Address what the load test surfaces</t>
-        </is>
-      </c>
-      <c r="D35" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>PostgREST as an ECS service</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>Phase 3 - Production Ready</t>
+          <t>Phase 4 - Self-hosted platform</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 7</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="inlineStr">
-        <is>
-          <t>Run the platform services on AWS instead of Supabase</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>GoTrue as an ECS service</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 1 done, 5 in progress.</t>
+          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -12603,7 +12603,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>PostgREST as an ECS service</t>
+          <t>Own the JWT secret and the API keys</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -12650,7 +12650,7 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>GoTrue as an ECS service</t>
+          <t>Routing and configuration cutover</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
+          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -12697,17 +12697,17 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C39" s="23" t="inlineStr">
         <is>
-          <t>Own the JWT secret and the API keys</t>
+          <t>Rehearse the cutover and the rollback</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
+          <t>Procedure written (docs/runbooks/platform-cutover.md) and the smoke test extended; the rehearsal itself needs the applied platform and Stage 5, Tasks 1 to 4.</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
@@ -12744,17 +12744,17 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>Routing and configuration cutover</t>
+          <t>Auth email through SES</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
+          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -12784,14 +12784,14 @@
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>Rehearse the cutover and the rollback</t>
+          <t>Carry the Google OAuth provider across</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>Procedure written (docs/runbooks/platform-cutover.md) and the smoke test extended; the rehearsal itself needs the applied platform and Stage 5, Tasks 1 to 4.</t>
+          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -12831,24 +12831,24 @@
       </c>
       <c r="I41" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>Auth email through SES</t>
+          <t>Cutover and decommission</t>
         </is>
       </c>
       <c r="D42" s="22" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="H42" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I42" s="20" t="inlineStr">
@@ -12885,7 +12885,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>Carry the Google OAuth provider across</t>
+          <t>Update the documentation</t>
         </is>
       </c>
       <c r="D43" s="22" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
+          <t>The platform is documented beside Supabase (plan row 5.10); the pass that removes the Supabase paragraphs waits for Stage 5, Task 6.</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -12920,129 +12920,35 @@
       </c>
       <c r="H43" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>2124</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C44" s="23" t="inlineStr">
-        <is>
-          <t>Cutover and decommission</t>
-        </is>
-      </c>
-      <c r="D44" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="inlineStr">
-        <is>
-          <t>Rolled up from 2 children: 2 in progress.</t>
-        </is>
-      </c>
-      <c r="F44" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G44" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H44" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I44" s="20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C45" s="23" t="inlineStr">
-        <is>
-          <t>Update the documentation</t>
-        </is>
-      </c>
-      <c r="D45" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="inlineStr">
-        <is>
-          <t>The platform is documented beside Supabase (plan row 5.10); the pass that removes the Supabase paragraphs waits for Stage 5, Task 6.</t>
-        </is>
-      </c>
-      <c r="F45" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G45" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H45" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I45" s="20" t="inlineStr">
-        <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Open tickets</t>
         </is>
       </c>
-      <c r="B47" s="7">
+      <c r="B45" s="7">
         <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>The rows are a snapshot; the count beside them is live from the Tickets sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I45"/>
+  <autoFilter ref="A4:I43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -5813,7 +5813,7 @@
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>rollback.yml exists; test-by-rolling-back needs a working deployment.</t>
+          <t>Drilled 18 September 2026: a broken deploy (unpullable image) was NOT rolled back by the ECS circuit breaker - it stalled IN_PROGRESS for 17 minutes and was restored by hand, so the "without manual intervention" criterion is not met. Availability held throughout (minimumHealthyPercent 100, 33/33 probes 200). The deploy workflow catches it instead. The runtime-failure case is still untested. See docs/runbooks/deploy-rolled-back.md.</t>
         </is>
       </c>
       <c r="G53" s="20" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>rollback.yml exists; test-by-rolling-back needs a working deployment.</t>
+          <t>Drilled 18 September 2026: a broken deploy (unpullable image) was NOT rolled back by the ECS circuit breaker - it stalled IN_PROGRESS for 17 minutes and was restored by hand, so the "without manual intervention" criterion is not met. Availability held throughout (minimumHealthyPercent 100, 33/33 probes 200). The deploy workflow catches it instead. The runtime-failure case is still untested. See docs/runbooks/deploy-rolled-back.md.</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">

--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -9738,14 +9738,14 @@
           <t>Post-launch monitoring window</t>
         </is>
       </c>
-      <c r="E108" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E108" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>Alarms are armed (16, all with actions) but both SNS alert topics have zero subscriptions, so nothing would reach anyone. Needs an address subscribed and confirmed before the window can start.</t>
+          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed to fraser@legalutopia.co.uk, and a test publish to each topic was confirmed received. What remains is the monitoring window itself passing with no unresolved incident, which is elapsed time not configuration.</t>
         </is>
       </c>
       <c r="G108" s="20" t="inlineStr">
@@ -12240,14 +12240,14 @@
           <t>Post-launch monitoring window</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>Alarms are armed (16, all with actions) but both SNS alert topics have zero subscriptions, so nothing would reach anyone. Needs an address subscribed and confirmed before the window can start.</t>
+          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed to fraser@legalutopia.co.uk, and a test publish to each topic was confirmed received. What remains is the monitoring window itself passing with no unresolved incident, which is elapsed time not configuration.</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">

--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tickets'!$A$1:$N$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5806,14 +5806,14 @@
           <t>Add health checks, rollback and deploy gating</t>
         </is>
       </c>
-      <c r="E53" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>Drilled 18 September 2026: a broken deploy (unpullable image) was NOT rolled back by the ECS circuit breaker - it stalled IN_PROGRESS for 17 minutes and was restored by hand, so the "without manual intervention" criterion is not met. Availability held throughout (minimumHealthyPercent 100, 33/33 probes 200). The deploy workflow catches it instead. The runtime-failure case is still untested. See docs/runbooks/deploy-rolled-back.md.</t>
+          <t>Drilled twice against production 18 September 2026. A runtime failure (real image, container runs but never listens on 3001) was caught by the ALB health check and rolled back by the ECS circuit breaker unaided after 3 failures - the acceptance criterion, met. A placement failure (unpullable image) is NOT caught by the breaker and stalls instead; the deploy workflow's wait services-stable catches that. Site 200 on all 60 probes. See docs/runbooks/deploy-rolled-back.md.</t>
         </is>
       </c>
       <c r="G53" s="20" t="inlineStr">
@@ -11021,7 +11021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11804,17 +11804,17 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>Add health checks, rollback and deploy gating</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Integration with the Juralio platform</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>Drilled 18 September 2026: a broken deploy (unpullable image) was NOT rolled back by the ECS circuit breaker - it stalled IN_PROGRESS for 17 minutes and was restored by hand, so the "without manual intervention" criterion is not met. Availability held throughout (minimumHealthyPercent 100, 33/33 probes 200). The deploy workflow catches it instead. The runtime-failure case is still untested. See docs/runbooks/deploy-rolled-back.md.</t>
+          <t>Rolled up from 2 children: 1 done, 1 deferred.</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -11834,34 +11834,34 @@
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>Integration with the Juralio platform</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>Backup, restore and disaster recovery</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -11871,22 +11871,22 @@
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 done, 1 deferred.</t>
+          <t>Rolled up from 2 children: 1 done, 1 in progress.</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Phase 2 - Infrastructure</t>
+          <t>Phase 3 - Production Ready</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 6</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -11898,17 +11898,17 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>Backup, restore and disaster recovery</t>
+          <t>Configure automated backups and prove a restore</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 done, 1 in progress.</t>
+          <t>From the delivery plan row that cites it.</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -11945,17 +11945,17 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>Configure automated backups and prove a restore</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Launch</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -11992,17 +11992,17 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>Launch</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>Pre-launch verification</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 in progress.</t>
+          <t>Rolled up from 3 children: 2 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -12039,27 +12039,27 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>Pre-launch verification</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Run the full suite against production configuration</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 2 in progress, 1 to do.</t>
+          <t>From the delivery plan row that cites it.</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
@@ -12096,17 +12096,17 @@
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>Run the full suite against production configuration</t>
-        </is>
-      </c>
-      <c r="D26" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Security review of the combined deployment</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>This repository half done: 3 findings, all fixed. Juralio side and the seam from its end outstanding.</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -12133,17 +12133,17 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>Security review of the combined deployment</t>
+          <t>Go live</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>This repository half done: 3 findings, all fixed. Juralio side and the seam from its end outstanding.</t>
+          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -12180,17 +12180,17 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>Go live</t>
+          <t>Post-launch monitoring window</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
+          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed to fraser@legalutopia.co.uk, and a test publish to each topic was confirmed received. What remains is the monitoring window itself passing with no unresolved incident, which is elapsed time not configuration.</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -12227,17 +12227,17 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>Post-launch monitoring window</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>Operational readiness</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed to fraser@legalutopia.co.uk, and a test publish to each topic was confirmed received. What remains is the monitoring window itself passing with no unresolved incident, which is elapsed time not configuration.</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -12262,29 +12262,29 @@
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>Operational readiness</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Performance and resilience</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 in progress.</t>
+          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -12309,29 +12309,29 @@
       </c>
       <c r="H30" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>Performance and resilience</t>
+          <t>Run the k6 SSE load scenario against staging</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
+          <t>As 2097.</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -12368,7 +12368,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
@@ -12378,17 +12378,17 @@
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>Run the k6 SSE load scenario against staging</t>
-        </is>
-      </c>
-      <c r="D32" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Address what the load test surfaces</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>As 2097.</t>
+          <t>From the delivery plan row that cites it.</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -12415,64 +12415,64 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>Address what the load test surfaces</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>Run the platform services on AWS instead of Supabase</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>Rolled up from 6 children: 1 done, 5 in progress.</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>Phase 3 - Production Ready</t>
+          <t>Phase 4 - Self-hosted platform</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 7</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>Run the platform services on AWS instead of Supabase</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>PostgREST as an ECS service</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 1 done, 5 in progress.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -12509,7 +12509,7 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>PostgREST as an ECS service</t>
+          <t>GoTrue as an ECS service</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
+          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -12556,7 +12556,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
-          <t>GoTrue as an ECS service</t>
+          <t>Own the JWT secret and the API keys</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -12603,7 +12603,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>Own the JWT secret and the API keys</t>
+          <t>Routing and configuration cutover</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
+          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -12650,17 +12650,17 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>Routing and configuration cutover</t>
+          <t>Rehearse the cutover and the rollback</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
+          <t>Procedure written (docs/runbooks/platform-cutover.md) and the smoke test extended; the rehearsal itself needs the applied platform and Stage 5, Tasks 1 to 4.</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -12697,7 +12697,7 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="C39" s="23" t="inlineStr">
         <is>
-          <t>Rehearse the cutover and the rollback</t>
+          <t>Auth email through SES</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>Procedure written (docs/runbooks/platform-cutover.md) and the smoke test extended; the rehearsal itself needs the applied platform and Stage 5, Tasks 1 to 4.</t>
+          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
@@ -12737,14 +12737,14 @@
       </c>
       <c r="I39" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>Auth email through SES</t>
+          <t>Carry the Google OAuth provider across</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
+          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -12791,17 +12791,17 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>Carry the Google OAuth provider across</t>
+          <t>Cutover and decommission</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="H41" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I41" s="20" t="inlineStr">
@@ -12838,17 +12838,17 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>Cutover and decommission</t>
+          <t>Update the documentation</t>
         </is>
       </c>
       <c r="D42" s="22" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 in progress.</t>
+          <t>The platform is documented beside Supabase (plan row 5.10); the pass that removes the Supabase paragraphs waits for Stage 5, Task 6.</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
@@ -12878,77 +12878,30 @@
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C43" s="23" t="inlineStr">
-        <is>
-          <t>Update the documentation</t>
-        </is>
-      </c>
-      <c r="D43" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>The platform is documented beside Supabase (plan row 5.10); the pass that removes the Supabase paragraphs waits for Stage 5, Task 6.</t>
-        </is>
-      </c>
-      <c r="F43" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G43" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H43" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I43" s="20" t="inlineStr">
-        <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Open tickets</t>
+        </is>
+      </c>
+      <c r="B44" s="7">
+        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
+        <v/>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Open tickets</t>
-        </is>
-      </c>
-      <c r="B45" s="7">
-        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>The rows are a snapshot; the count beside them is live from the Tickets sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I43"/>
+  <autoFilter ref="A4:I42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -9745,7 +9745,7 @@
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed to fraser@legalutopia.co.uk, and a test publish to each topic was confirmed received. What remains is the monitoring window itself passing with no unresolved incident, which is elapsed time not configuration.</t>
+          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed, and a test publish to each topic was confirmed received. The subscriptions are account state, not Terraform: alert_email is now documented in terraform.tfvars.example and the module README carries the import commands that adopt the existing pair instead of duplicating them. Remaining: the monitoring window itself.</t>
         </is>
       </c>
       <c r="G108" s="20" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed to fraser@legalutopia.co.uk, and a test publish to each topic was confirmed received. What remains is the monitoring window itself passing with no unresolved incident, which is elapsed time not configuration.</t>
+          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed, and a test publish to each topic was confirmed received. The subscriptions are account state, not Terraform: alert_email is now documented in terraform.tfvars.example and the module README carries the import commands that adopt the existing pair instead of duplicating them. Remaining: the monitoring window itself.</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">

--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tickets'!$A$1:$N$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -68,12 +68,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00434343"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="000B5394"/>
       <sz val="10"/>
     </font>
@@ -81,6 +75,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00674EA7"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00434343"/>
       <sz val="10"/>
     </font>
     <font>
@@ -131,17 +131,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EAED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00CFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EAED"/>
       </patternFill>
     </fill>
   </fills>
@@ -205,13 +205,13 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3086,14 +3086,14 @@
           <t>Take ownership of the workflow catalogue</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 to do.</t>
+          <t>Rolled up from 2 children: 2 done.</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -3158,14 +3158,14 @@
           <t>Fork mike-workflows and repoint the sync</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Licence checked 17 September 2026: the catalogue repository is MIT (outstanding.md). The fork itself needs an account only the operator controls; after it, two tfvars values and an apply.</t>
+          <t>Forked to Fraser-Matcham/mike-workflows and pinned at ce62e6a2. workflows_repository and workflows_ref applied; backend task definition :22 carries MIKE_WORKFLOWS_REPOSITORY=Fraser-Matcham/mike-workflows, replacing Open-Legal-Products on :20.</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -3230,14 +3230,14 @@
           <t>Verify catalogue sync end to end</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>Inherited from parent 2014 (to do).</t>
+          <t>Proved by deploy run 37 on 18 September 2026: the catalogue-sync task ran from revision :22 against the fork and exited clean, the service rolled COMPLETED 1/1, and readiness passed through the edge.</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -4802,7 +4802,7 @@
           <t>Provision Supabase and load the schema</t>
         </is>
       </c>
-      <c r="E39" s="27" t="inlineStr">
+      <c r="E39" s="26" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -4874,7 +4874,7 @@
           <t>Create staging and production Supabase projects</t>
         </is>
       </c>
-      <c r="E40" s="27" t="inlineStr">
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -4946,7 +4946,7 @@
           <t>Load the schema and verify RLS is deny-all</t>
         </is>
       </c>
-      <c r="E41" s="27" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -5018,7 +5018,7 @@
           <t>Configure auth: providers, email delivery and MFA</t>
         </is>
       </c>
-      <c r="E42" s="27" t="inlineStr">
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -5234,14 +5234,14 @@
           <t>Verify the signed-URL round trip</t>
         </is>
       </c>
-      <c r="E45" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>Code half done and tested (storageRegion.ts). Live check needs the deployed stack.</t>
+          <t>Signed-URL round trip proven against the live stack on 18 September 2026. A document uploaded through the product downloaded again with its contents intact, and the objects were confirmed in legalworkflows-production-documents (KMS-encrypted, real sizes) rather than taken from the UI. R2_REGION eu-west-2 matches the bucket's own region, which is what storageRegion.ts resolves the signing region from.</t>
         </is>
       </c>
       <c r="G45" s="20" t="inlineStr">
@@ -6806,7 +6806,7 @@
           <t>Build the HTTP client seam in Juralio</t>
         </is>
       </c>
-      <c r="E67" s="28" t="inlineStr">
+      <c r="E67" s="27" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -6878,7 +6878,7 @@
           <t>Write Juralio's proxy to the workflow service</t>
         </is>
       </c>
-      <c r="E68" s="28" t="inlineStr">
+      <c r="E68" s="27" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -6950,7 +6950,7 @@
           <t>Re-declare the API types on the Juralio side</t>
         </is>
       </c>
-      <c r="E69" s="28" t="inlineStr">
+      <c r="E69" s="27" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -7022,7 +7022,7 @@
           <t>Map identity and sessions between the two systems</t>
         </is>
       </c>
-      <c r="E70" s="28" t="inlineStr">
+      <c r="E70" s="27" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
@@ -9166,7 +9166,7 @@
           <t>Address what the load test surfaces</t>
         </is>
       </c>
-      <c r="E100" s="26" t="inlineStr">
+      <c r="E100" s="28" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9378,7 +9378,7 @@
           <t>Run the full suite against production configuration</t>
         </is>
       </c>
-      <c r="E103" s="26" t="inlineStr">
+      <c r="E103" s="28" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11021,7 +11021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11240,27 +11240,27 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>Take ownership of the workflow catalogue</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Run a first upstream merge as a dry run</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 to do.</t>
+          <t>Rehearsed in a scratch worktree on 17 September 2026 and sized in docs/upstream-sync.md ("The first sync, sized"): 49 conflicts, four of them decisions against fork positions, plus 40 files to debrand. Recommended as its own sprint.</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -11275,39 +11275,39 @@
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>Fork mike-workflows and repoint the sync</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>CI/CD adaptation</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>Licence checked 17 September 2026: the catalogue repository is MIT (outstanding.md). The fork itself needs an account only the operator controls; after it, two tfvars values and an apply.</t>
+          <t>Rolled up from 2 children: 1 done, 1 in progress.</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -11317,34 +11317,34 @@
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Run a first upstream merge as a dry run</t>
+          <t>Port the inherited workflows to the private repo</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Rehearsed in a scratch worktree on 17 September 2026 and sized in docs/upstream-sync.md ("The first sync, sized"): 49 conflicts, four of them decisions against fork positions, plus 40 files to debrand. Recommended as its own sprint.</t>
+          <t>Rolled up from 5 children: 3 done, 1 in progress, 1 won't do.</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -11374,14 +11374,14 @@
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -11391,17 +11391,17 @@
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>Verify catalogue sync end to end</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Configure Actions secrets and verify the e2e run</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>Inherited from parent 2014 (to do).</t>
+          <t>e2e green, but ANTHROPIC_API_KEY is unset so 4 LLM specs — including critical-path "ask a question" — skip every run. Established from the job env block.</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -11411,24 +11411,24 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>CI/CD adaptation</t>
+          <t>Infrastructure foundation</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -11448,22 +11448,22 @@
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 done, 1 in progress.</t>
+          <t>Rolled up from 3 children: 1 done, 1 in progress, 1 superseded.</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Phase 1 - Extraction</t>
+          <t>Phase 2 - Infrastructure</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -11475,7 +11475,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>Port the inherited workflows to the private repo</t>
+          <t>Provision object storage</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -11495,22 +11495,22 @@
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 5 children: 3 done, 1 in progress, 1 won't do.</t>
+          <t>Rolled up from 2 children: 1 done, 1 in progress.</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Phase 1 - Extraction</t>
+          <t>Phase 2 - Infrastructure</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -11522,17 +11522,17 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>Configure Actions secrets and verify the e2e run</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Deployment pipeline</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -11542,44 +11542,44 @@
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>e2e green, but ANTHROPIC_API_KEY is unset so 4 LLM specs — including critical-path "ask a question" — skip every run. Established from the job env block.</t>
+          <t>Rolled up from 2 children: 1 done, 1 in progress.</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Phase 1 - Extraction</t>
+          <t>Phase 2 - Infrastructure</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>Infrastructure foundation</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Containerise and deploy the backend</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 1 done, 1 in progress, 1 superseded.</t>
+          <t>Rolled up from 3 children: 2 done, 1 in progress.</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -11616,17 +11616,17 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>Provision object storage</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>Integration with the Juralio platform</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 done, 1 in progress.</t>
+          <t>Rolled up from 2 children: 1 done, 1 deferred.</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -11646,12 +11646,12 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -11663,17 +11663,17 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>Deployment pipeline</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>Backup, restore and disaster recovery</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -11688,12 +11688,12 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Phase 2 - Infrastructure</t>
+          <t>Phase 3 - Production Ready</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 6</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -11710,17 +11710,17 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>Containerise and deploy the backend</t>
+          <t>Configure automated backups and prove a restore</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -11730,17 +11730,17 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 2 done, 1 in progress.</t>
+          <t>From the delivery plan row that cites it.</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Phase 2 - Infrastructure</t>
+          <t>Phase 3 - Production Ready</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 6</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -11757,17 +11757,17 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>Verify the signed-URL round trip</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Launch</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -11777,44 +11777,44 @@
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>Code half done and tested (storageRegion.ts). Live check needs the deployed stack.</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Phase 2 - Infrastructure</t>
+          <t>Phase 3 - Production Ready</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 6</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>Integration with the Juralio platform</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>Pre-launch verification</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -11824,22 +11824,22 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 done, 1 deferred.</t>
+          <t>Rolled up from 3 children: 2 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>Phase 2 - Infrastructure</t>
+          <t>Phase 3 - Production Ready</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 6</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -11851,27 +11851,27 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>Backup, restore and disaster recovery</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Run the full suite against production configuration</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 done, 1 in progress.</t>
+          <t>From the delivery plan row that cites it.</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -11898,7 +11898,7 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>Configure automated backups and prove a restore</t>
+          <t>Security review of the combined deployment</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>This repository half done: 3 findings, all fixed. Juralio side and the seam from its end outstanding.</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -11945,17 +11945,17 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>Launch</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>Go live</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 in progress.</t>
+          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -11992,17 +11992,17 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>Pre-launch verification</t>
+          <t>Post-launch monitoring window</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 2 in progress, 1 to do.</t>
+          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed, and a test publish to each topic was confirmed received. The subscriptions are account state, not Terraform: alert_email is now documented in terraform.tfvars.example and the module README carries the import commands that adopt the existing pair instead of duplicating them. Remaining: the monitoring window itself.</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -12039,27 +12039,27 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>Run the full suite against production configuration</t>
-        </is>
-      </c>
-      <c r="D25" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>Operational readiness</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -12074,29 +12074,29 @@
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>Security review of the combined deployment</t>
+          <t>Performance and resilience</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>This repository half done: 3 findings, all fixed. Juralio side and the seam from its end outstanding.</t>
+          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -12121,29 +12121,29 @@
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>Go live</t>
+          <t>Run the k6 SSE load scenario against staging</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
+          <t>As 2097.</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -12168,19 +12168,19 @@
       </c>
       <c r="H27" s="20" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
@@ -12190,17 +12190,17 @@
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>Post-launch monitoring window</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Address what the load test surfaces</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed, and a test publish to each topic was confirmed received. The subscriptions are account state, not Terraform: alert_email is now documented in terraform.tfvars.example and the module README carries the import commands that adopt the existing pair instead of duplicating them. Remaining: the monitoring window itself.</t>
+          <t>From the delivery plan row that cites it.</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -12215,19 +12215,19 @@
       </c>
       <c r="H28" s="20" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>Operational readiness</t>
+          <t>Run the platform services on AWS instead of Supabase</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -12247,17 +12247,17 @@
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 in progress.</t>
+          <t>Rolled up from 6 children: 1 done, 5 in progress.</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>Phase 3 - Production Ready</t>
+          <t>Phase 4 - Self-hosted platform</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 7</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -12267,14 +12267,14 @@
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>Performance and resilience</t>
+          <t>PostgREST as an ECS service</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -12294,44 +12294,44 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>Phase 3 - Production Ready</t>
+          <t>Phase 4 - Self-hosted platform</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 7</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>Run the k6 SSE load scenario against staging</t>
+          <t>GoTrue as an ECS service</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -12341,91 +12341,91 @@
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>As 2097.</t>
+          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>Phase 3 - Production Ready</t>
+          <t>Phase 4 - Self-hosted platform</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 7</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>Address what the load test surfaces</t>
-        </is>
-      </c>
-      <c r="D32" s="26" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Own the JWT secret and the API keys</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>Phase 3 - Production Ready</t>
+          <t>Phase 4 - Self-hosted platform</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 7</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="inlineStr">
-        <is>
-          <t>Run the platform services on AWS instead of Supabase</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>Routing and configuration cutover</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 1 done, 5 in progress.</t>
+          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -12462,17 +12462,17 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>PostgREST as an ECS service</t>
+          <t>Rehearse the cutover and the rollback</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
+          <t>Procedure written (docs/runbooks/platform-cutover.md) and the smoke test extended; the rehearsal itself needs the applied platform and Stage 5, Tasks 1 to 4.</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -12509,17 +12509,17 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>GoTrue as an ECS service</t>
+          <t>Auth email through SES</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
+          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -12549,24 +12549,24 @@
       </c>
       <c r="I35" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
-          <t>Own the JWT secret and the API keys</t>
+          <t>Carry the Google OAuth provider across</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
+          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -12596,14 +12596,14 @@
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>Routing and configuration cutover</t>
+          <t>Cutover and decommission</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -12638,19 +12638,19 @@
       </c>
       <c r="H37" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>Rehearse the cutover and the rollback</t>
+          <t>Update the documentation</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>Procedure written (docs/runbooks/platform-cutover.md) and the smoke test extended; the rehearsal itself needs the applied platform and Stage 5, Tasks 1 to 4.</t>
+          <t>The platform is documented beside Supabase (plan row 5.10); the pass that removes the Supabase paragraphs waits for Stage 5, Task 6.</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -12685,223 +12685,35 @@
       </c>
       <c r="H38" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>Auth email through SES</t>
-        </is>
-      </c>
-      <c r="D39" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
-        </is>
-      </c>
-      <c r="F39" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G39" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H39" s="20" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="I39" s="20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>2119</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>Carry the Google OAuth provider across</t>
-        </is>
-      </c>
-      <c r="D40" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G40" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H40" s="20" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="I40" s="20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>2124</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>Cutover and decommission</t>
-        </is>
-      </c>
-      <c r="D41" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>Rolled up from 2 children: 2 in progress.</t>
-        </is>
-      </c>
-      <c r="F41" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G41" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H41" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I41" s="20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="inlineStr">
-        <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="inlineStr">
-        <is>
-          <t>Update the documentation</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>The platform is documented beside Supabase (plan row 5.10); the pass that removes the Supabase paragraphs waits for Stage 5, Task 6.</t>
-        </is>
-      </c>
-      <c r="F42" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G42" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H42" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I42" s="20" t="inlineStr">
-        <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Open tickets</t>
         </is>
       </c>
-      <c r="B44" s="7">
+      <c r="B40" s="7">
         <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>The rows are a snapshot; the count beside them is live from the Tickets sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I42"/>
+  <autoFilter ref="A4:I38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -8885,7 +8885,7 @@
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>Drilled 18 September 2026, partial. Documents passed: a document deleted from production was recovered from the backup bucket by version id, size and ETag matching, and live/backup are identical across all 8 objects with every one ReplicationStatus COMPLETED. Database could not be attempted: the Supabase org is on the Free plan, which has no accessible daily backups, and no self-managed dump exists. Stays open until the database has a backup and the application can be run against restored data.</t>
         </is>
       </c>
       <c r="G96" s="20" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>As 2097.</t>
+          <t>Blocked on Task 3 (2020): without a provider key the SSE scenario measures how fast the service fails. Also needs a LOADTEST_AUTH_TOKEN and a decision on which stack to point at, since every iteration writes a real chat row and spends real tokens.</t>
         </is>
       </c>
       <c r="G99" s="20" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>Drilled 18 September 2026, partial. Documents passed: a document deleted from production was recovered from the backup bucket by version id, size and ETag matching, and live/backup are identical across all 8 objects with every one ReplicationStatus COMPLETED. Database could not be attempted: the Supabase org is on the Free plan, which has no accessible daily backups, and no self-managed dump exists. Stays open until the database has a backup and the application can be run against restored data.</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>As 2097.</t>
+          <t>Blocked on Task 3 (2020): without a provider key the SSE scenario measures how fast the service fails. Also needs a LOADTEST_AUTH_TOKEN and a decision on which stack to point at, since every iteration writes a real chat row and spends real tokens.</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">

--- a/docs/delivery-plan/v2/delivery-status.xlsx
+++ b/docs/delivery-plan/v2/delivery-status.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tickets'!$A$1:$N$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Outstanding'!$A$4:$I$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -74,12 +74,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00674EA7"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00434343"/>
       <sz val="10"/>
     </font>
@@ -100,6 +94,12 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00674EA7"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -136,12 +136,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
+        <fgColor rgb="00E8EAED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EAED"/>
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,11 +171,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -205,10 +205,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,7 +217,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -242,9 +242,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1972,7 +1969,7 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Replaced by the stage 5 move off Supabase; the work no longer applies.</t>
+          <t>Replaced by a later decision: stage 5 (off Supabase) or architecture decision 7 (fold-in, not a Juralio HTTP seam).</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2009,7 @@
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>- The twelve tickets with no marker are resolved explicitly by the plan's ticket disposition table (2023 won't do; 2029-2031 done; 2038-2041 superseded by stage 5; 2066-2069 deferred).</t>
+          <t>- The twelve tickets with no marker are resolved explicitly by the plan's ticket disposition table (2023 won't do; 2029-2031 done; 2038-2041 superseded by stage 5; 2066-2069 cancelled by architecture decision 7).</t>
         </is>
       </c>
     </row>
@@ -6734,14 +6731,14 @@
           <t>Integration with the Juralio platform</t>
         </is>
       </c>
-      <c r="E66" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="E66" s="26" t="inlineStr">
+        <is>
+          <t>Superseded</t>
         </is>
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 done, 1 deferred.</t>
+          <t>Epic kept as the licence-boundary record. Child 2070 (boundary CI) shipped and stays Done. HTTP seam children 2066–2069 cancelled — architecture decision 7.</t>
         </is>
       </c>
       <c r="G66" s="20" t="inlineStr">
@@ -6806,14 +6803,14 @@
           <t>Build the HTTP client seam in Juralio</t>
         </is>
       </c>
-      <c r="E67" s="27" t="inlineStr">
-        <is>
-          <t>Deferred</t>
+      <c r="E67" s="26" t="inlineStr">
+        <is>
+          <t>Superseded</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 3 deferred.</t>
+          <t>HTTP client seam in Juralio cancelled. Reimplement matter features in this origin (architecture decision 7).</t>
         </is>
       </c>
       <c r="G67" s="20" t="inlineStr">
@@ -6878,9 +6875,9 @@
           <t>Write Juralio's proxy to the workflow service</t>
         </is>
       </c>
-      <c r="E68" s="27" t="inlineStr">
-        <is>
-          <t>Deferred</t>
+      <c r="E68" s="26" t="inlineStr">
+        <is>
+          <t>Superseded</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr">
@@ -6950,9 +6947,9 @@
           <t>Re-declare the API types on the Juralio side</t>
         </is>
       </c>
-      <c r="E69" s="27" t="inlineStr">
-        <is>
-          <t>Deferred</t>
+      <c r="E69" s="26" t="inlineStr">
+        <is>
+          <t>Superseded</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
@@ -7022,9 +7019,9 @@
           <t>Map identity and sessions between the two systems</t>
         </is>
       </c>
-      <c r="E70" s="27" t="inlineStr">
-        <is>
-          <t>Deferred</t>
+      <c r="E70" s="26" t="inlineStr">
+        <is>
+          <t>Superseded</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
@@ -7101,7 +7098,7 @@
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done.</t>
+          <t>Boundary CI shipped (`npm run boundary`). Seam itself superseded: fold-in (architecture decision 7). Keep the CI.</t>
         </is>
       </c>
       <c r="G71" s="20" t="inlineStr">
@@ -9166,7 +9163,7 @@
           <t>Address what the load test surfaces</t>
         </is>
       </c>
-      <c r="E100" s="28" t="inlineStr">
+      <c r="E100" s="27" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -9378,7 +9375,7 @@
           <t>Run the full suite against production configuration</t>
         </is>
       </c>
-      <c r="E103" s="28" t="inlineStr">
+      <c r="E103" s="27" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
@@ -11021,7 +11018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11616,17 +11613,17 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>Integration with the Juralio platform</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>Backup, restore and disaster recovery</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -11636,22 +11633,22 @@
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 done, 1 deferred.</t>
+          <t>Rolled up from 2 children: 1 done, 1 in progress.</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Phase 2 - Infrastructure</t>
+          <t>Phase 3 - Production Ready</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 6</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -11663,17 +11660,17 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>Backup, restore and disaster recovery</t>
+          <t>Configure automated backups and prove a restore</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -11683,7 +11680,7 @@
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 done, 1 in progress.</t>
+          <t>Drilled 18 September 2026, partial. Documents passed: a document deleted from production was recovered from the backup bucket by version id, size and ETag matching, and live/backup are identical across all 8 objects with every one ReplicationStatus COMPLETED. Database could not be attempted: the Supabase org is on the Free plan, which has no accessible daily backups, and no self-managed dump exists. Stays open until the database has a backup and the application can be run against restored data.</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -11710,17 +11707,17 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>Configure automated backups and prove a restore</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Launch</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -11730,7 +11727,7 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>Drilled 18 September 2026, partial. Documents passed: a document deleted from production was recovered from the backup bucket by version id, size and ETag matching, and live/backup are identical across all 8 objects with every one ReplicationStatus COMPLETED. Database could not be attempted: the Supabase org is on the Free plan, which has no accessible daily backups, and no self-managed dump exists. Stays open until the database has a backup and the application can be run against restored data.</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -11745,7 +11742,7 @@
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -11757,17 +11754,17 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>Launch</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Pre-launch verification</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -11777,7 +11774,7 @@
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 in progress.</t>
+          <t>Rolled up from 3 children: 2 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -11804,27 +11801,27 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>Pre-launch verification</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Run the full suite against production configuration</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 2 in progress, 1 to do.</t>
+          <t>From the delivery plan row that cites it.</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -11851,7 +11848,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -11861,17 +11858,17 @@
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>Run the full suite against production configuration</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Security review of the combined deployment</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>This repository half done: 3 findings, all fixed. Juralio side and the seam from its end outstanding.</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -11898,17 +11895,17 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>Security review of the combined deployment</t>
+          <t>Go live</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -11918,7 +11915,7 @@
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>This repository half done: 3 findings, all fixed. Juralio side and the seam from its end outstanding.</t>
+          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -11945,17 +11942,17 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>Go live</t>
+          <t>Post-launch monitoring window</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -11965,7 +11962,7 @@
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
+          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed, and a test publish to each topic was confirmed received. The subscriptions are account state, not Terraform: alert_email is now documented in terraform.tfvars.example and the module README carries the import commands that adopt the existing pair instead of duplicating them. Remaining: the monitoring window itself.</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -11992,17 +11989,17 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>Post-launch monitoring window</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>Operational readiness</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -12012,7 +12009,7 @@
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>Alerting proven working 18 September 2026: both SNS alert topics had zero subscriptions, so all 16 alarms fired into silence. Subscribed and confirmed, and a test publish to each topic was confirmed received. The subscriptions are account state, not Terraform: alert_email is now documented in terraform.tfvars.example and the module README carries the import commands that adopt the existing pair instead of duplicating them. Remaining: the monitoring window itself.</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -12027,29 +12024,29 @@
       </c>
       <c r="H24" s="20" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>Operational readiness</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>Performance and resilience</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -12059,7 +12056,7 @@
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 in progress.</t>
+          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -12074,29 +12071,29 @@
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>Performance and resilience</t>
+          <t>Run the k6 SSE load scenario against staging</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -12106,7 +12103,7 @@
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 1 in progress, 1 to do.</t>
+          <t>Blocked on Task 3 (2020): without a provider key the SSE scenario measures how fast the service fails. Also needs a LOADTEST_AUTH_TOKEN and a decision on which stack to point at, since every iteration writes a real chat row and spends real tokens.</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -12133,7 +12130,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -12143,17 +12140,17 @@
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>Run the k6 SSE load scenario against staging</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>Address what the load test surfaces</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>To do</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>Blocked on Task 3 (2020): without a provider key the SSE scenario measures how fast the service fails. Also needs a LOADTEST_AUTH_TOKEN and a decision on which stack to point at, since every iteration writes a real chat row and spends real tokens.</t>
+          <t>From the delivery plan row that cites it.</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -12180,64 +12177,64 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>Address what the load test surfaces</t>
-        </is>
-      </c>
-      <c r="D28" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Run the platform services on AWS instead of Supabase</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>From the delivery plan row that cites it.</t>
+          <t>Rolled up from 6 children: 1 done, 5 in progress.</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Phase 3 - Production Ready</t>
+          <t>Phase 4 - Self-hosted platform</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 7</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>Run the platform services on AWS instead of Supabase</t>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>PostgREST as an ECS service</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -12247,7 +12244,7 @@
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 6 children: 1 done, 5 in progress.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -12274,7 +12271,7 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
@@ -12284,7 +12281,7 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>PostgREST as an ECS service</t>
+          <t>GoTrue as an ECS service</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -12294,7 +12291,7 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the backend's queries succeed against the self-hosted endpoint after cutover.</t>
+          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -12321,7 +12318,7 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -12331,7 +12328,7 @@
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>GoTrue as an ECS service</t>
+          <t>Own the JWT secret and the API keys</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -12341,7 +12338,7 @@
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 3 children: 1 done, 2 in progress.</t>
+          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -12368,7 +12365,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
@@ -12378,7 +12375,7 @@
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>Own the JWT secret and the API keys</t>
+          <t>Routing and configuration cutover</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -12388,7 +12385,7 @@
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. Closes when the runbook has been walked once against the applied footprint.</t>
+          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -12415,17 +12412,17 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>Routing and configuration cutover</t>
+          <t>Rehearse the cutover and the rollback</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -12435,7 +12432,7 @@
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 1 child: 1 done. The platform_serves_backend switch exists; closes at the cutover.</t>
+          <t>Procedure written (docs/runbooks/platform-cutover.md) and the smoke test extended; the rehearsal itself needs the applied platform and Stage 5, Tasks 1 to 4.</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -12462,7 +12459,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
@@ -12472,7 +12469,7 @@
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>Rehearse the cutover and the rollback</t>
+          <t>Auth email through SES</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -12482,7 +12479,7 @@
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>Procedure written (docs/runbooks/platform-cutover.md) and the smoke test extended; the rehearsal itself needs the applied platform and Stage 5, Tasks 1 to 4.</t>
+          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -12502,14 +12499,14 @@
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -12519,7 +12516,7 @@
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>Auth email through SES</t>
+          <t>Carry the Google OAuth provider across</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -12529,7 +12526,7 @@
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>Wired to the email module's SES credential (plan row 5.5); the deliverability check needs the running service.</t>
+          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -12556,17 +12553,17 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
-          <t>Carry the Google OAuth provider across</t>
+          <t>Cutover and decommission</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -12576,7 +12573,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Provider, secret container and redirect URI in place (plan row 5.6); the operator adds the URI and writes the client (Stage 5, Task 3).</t>
+          <t>Rolled up from 2 children: 2 in progress.</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -12591,7 +12588,7 @@
       </c>
       <c r="H36" s="20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="I36" s="20" t="inlineStr">
@@ -12603,17 +12600,17 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Sub-task</t>
         </is>
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>Cutover and decommission</t>
+          <t>Update the documentation</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -12623,7 +12620,7 @@
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>Rolled up from 2 children: 2 in progress.</t>
+          <t>The platform is documented beside Supabase (plan row 5.10); the pass that removes the Supabase paragraphs waits for Stage 5, Task 6.</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -12643,77 +12640,30 @@
       </c>
       <c r="I37" s="20" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>Sub-task</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>Update the documentation</t>
-        </is>
-      </c>
-      <c r="D38" s="22" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="inlineStr">
-        <is>
-          <t>The platform is documented beside Supabase (plan row 5.10); the pass that removes the Supabase paragraphs waits for Stage 5, Task 6.</t>
-        </is>
-      </c>
-      <c r="F38" s="20" t="inlineStr">
-        <is>
-          <t>Phase 4 - Self-hosted platform</t>
-        </is>
-      </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H38" s="20" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="I38" s="20" t="inlineStr">
-        <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Open tickets</t>
+        </is>
+      </c>
+      <c r="B39" s="7">
+        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
+        <v/>
+      </c>
+    </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Open tickets</t>
-        </is>
-      </c>
-      <c r="B40" s="7">
-        <f>COUNTIF(Tickets!$E$2:$E$125,"In progress")+COUNTIF(Tickets!$E$2:$E$125,"To do")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>The rows are a snapshot; the count beside them is live from the Tickets sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I38"/>
+  <autoFilter ref="A4:I37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>